--- a/Analysed/Gemini/Analysis_Summary_Depth_without_vernier_flash.xlsx
+++ b/Analysed/Gemini/Analysis_Summary_Depth_without_vernier_flash.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7.2617 ± 0.1665</t>
+          <t>14.7904 ± 8.1923</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8.2370 ± 0.9996</t>
+          <t>17.3076 ± 8.7714</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.9462 ± 0.0195</t>
+          <t>0.9247 ± 0.0383</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,38 +521,114 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V1_5 divisions_per_second</t>
+          <t>V2_0.5 divisions_per_second</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="C2" t="n">
-        <v>7.144000000000001</v>
+        <v>12.56611111111111</v>
       </c>
       <c r="D2" t="n">
-        <v>7.530228150594111</v>
+        <v>16.01832846539853</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9324324324324325</v>
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V2_10 divisions_per_second</t>
+          <t>V3_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>82</v>
+      </c>
+      <c r="C3" t="n">
+        <v>19.04268292682927</v>
+      </c>
+      <c r="D3" t="n">
+        <v>21.94403252400602</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>V4_1.7 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>55</v>
+      </c>
+      <c r="C4" t="n">
+        <v>28.86381818181817</v>
+      </c>
+      <c r="D4" t="n">
+        <v>31.28271457065533</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8703703703703703</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>V5_2.5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>45</v>
+      </c>
+      <c r="C5" t="n">
+        <v>13.74622222222222</v>
+      </c>
+      <c r="D5" t="n">
+        <v>18.12664312858592</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.8863636363636364</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>V6_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>75</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7.144000000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7.530228150594111</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9324324324324325</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>V7_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>51</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C7" t="n">
         <v>7.379411764705883</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D7" t="n">
         <v>8.94383619496427</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E7" t="n">
         <v>0.96</v>
       </c>
     </row>
